--- a/output/xlsx/CRUDSecao--GT-.xlsx
+++ b/output/xlsx/CRUDSecao--GT-.xlsx
@@ -92,25 +92,25 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>superAdmin: seleciona opcao 'Sections' no menu Settings</t>
+    <t>superAdmin: seleciona opção 'Sections' no menu Settings</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe lista de Secoes</t>
-  </si>
-  <si>
-    <t>superAdmin: clica no nome de uma secao</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe dados da secao</t>
-  </si>
-  <si>
-    <t>superAdmin: clica no botao 'Cancel'</t>
-  </si>
-  <si>
-    <t>SYSTEM retorna a lista de secoes</t>
+    <t>SYSTEM exibe lista de Seções</t>
+  </si>
+  <si>
+    <t>superAdmin: clica no nome de uma seção</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe dados da seção</t>
+  </si>
+  <si>
+    <t>superAdmin: clica no botão 'Cancel'</t>
+  </si>
+  <si>
+    <t>SYSTEM retorna a lista de seções</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -125,13 +125,13 @@
     <t>superAdmin: clica no botão 'Edit'</t>
   </si>
   <si>
-    <t>SYSTEM lista as opcoes possíveis de serem incluidas na secao</t>
-  </si>
-  <si>
-    <t>superAdmin: escolhe as opcoes e pressiona o botão 'Update</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe mensagem informando que a secao foi atualizada</t>
+    <t>SYSTEM lista as opções possíveis de serem incluídas na seção</t>
+  </si>
+  <si>
+    <t>superAdmin: escolhe as opções e pressiona o botão 'Update</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe mensagem informando que a seção foi atualizada</t>
   </si>
 </sst>
 </file>
